--- a/AnalysePharma/ig/StructureDefinition-fr-medicationrequest.xlsx
+++ b/AnalysePharma/ig/StructureDefinition-fr-medicationrequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-12T09:56:07+00:00</t>
+    <t>2026-02-16T16:30:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/AnalysePharma/ig/StructureDefinition-fr-medicationrequest.xlsx
+++ b/AnalysePharma/ig/StructureDefinition-fr-medicationrequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-16T16:30:02+00:00</t>
+    <t>2026-02-16T17:09:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/AnalysePharma/ig/StructureDefinition-fr-medicationrequest.xlsx
+++ b/AnalysePharma/ig/StructureDefinition-fr-medicationrequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-16T17:09:53+00:00</t>
+    <t>2026-02-17T08:04:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/AnalysePharma/ig/StructureDefinition-fr-medicationrequest.xlsx
+++ b/AnalysePharma/ig/StructureDefinition-fr-medicationrequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-17T08:04:39+00:00</t>
+    <t>2026-02-17T08:46:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/AnalysePharma/ig/StructureDefinition-fr-medicationrequest.xlsx
+++ b/AnalysePharma/ig/StructureDefinition-fr-medicationrequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-17T08:46:02+00:00</t>
+    <t>2026-02-17T09:04:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/AnalysePharma/ig/StructureDefinition-fr-medicationrequest.xlsx
+++ b/AnalysePharma/ig/StructureDefinition-fr-medicationrequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-17T09:04:14+00:00</t>
+    <t>2026-02-17T09:55:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/AnalysePharma/ig/StructureDefinition-fr-medicationrequest.xlsx
+++ b/AnalysePharma/ig/StructureDefinition-fr-medicationrequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-17T09:55:45+00:00</t>
+    <t>2026-02-17T10:22:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/AnalysePharma/ig/StructureDefinition-fr-medicationrequest.xlsx
+++ b/AnalysePharma/ig/StructureDefinition-fr-medicationrequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-17T10:22:56+00:00</t>
+    <t>2026-04-14T15:08:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/AnalysePharma/ig/StructureDefinition-fr-medicationrequest.xlsx
+++ b/AnalysePharma/ig/StructureDefinition-fr-medicationrequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-14T15:08:12+00:00</t>
+    <t>2026-04-14T15:34:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/AnalysePharma/ig/StructureDefinition-fr-medicationrequest.xlsx
+++ b/AnalysePharma/ig/StructureDefinition-fr-medicationrequest.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4792" uniqueCount="810">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4793" uniqueCount="811">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-14T15:34:16+00:00</t>
+    <t>2026-04-30T09:49:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -469,7 +469,11 @@
     <t>Full representation of the dosage instructions</t>
   </si>
   <si>
-    <t>Optional Extension Element - found in all resources.</t>
+    <t>R5: `MedicationRequest.renderedDosageInstruction` (new:markdown)</t>
+  </si>
+  <si>
+    <t>Element `MedicationRequest.renderedDosageInstruction` has a context of MedicationRequest based on following the parent source element upwards and mapping to `MedicationRequest`.
+Element `MedicationRequest.renderedDosageInstruction` has no mapping targets in FHIR R4. Typically, this is because the element has been added (is a new element).</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1
@@ -3969,7 +3973,9 @@
       <c r="M10" t="s" s="2">
         <v>146</v>
       </c>
-      <c r="N10" s="2"/>
+      <c r="N10" t="s" s="2">
+        <v>147</v>
+      </c>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
         <v>81</v>
@@ -4027,7 +4033,7 @@
         <v>80</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AJ10" t="s" s="2">
         <v>141</v>
@@ -4039,7 +4045,7 @@
         <v>81</v>
       </c>
       <c r="AM10" t="s" s="2">
-        <v>133</v>
+        <v>81</v>
       </c>
       <c r="AN10" t="s" s="2">
         <v>81</v>
@@ -4050,13 +4056,13 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B11" t="s" s="2">
         <v>134</v>
       </c>
       <c r="C11" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D11" t="s" s="2">
         <v>81</v>
@@ -4078,13 +4084,13 @@
         <v>81</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -4144,7 +4150,7 @@
         <v>80</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AJ11" t="s" s="2">
         <v>141</v>
@@ -4167,10 +4173,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -4193,13 +4199,13 @@
         <v>81</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -4250,7 +4256,7 @@
         <v>81</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>79</v>
@@ -4271,7 +4277,7 @@
         <v>81</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AN12" t="s" s="2">
         <v>81</v>
@@ -4282,10 +4288,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -4356,7 +4362,7 @@
         <v>138</v>
       </c>
       <c r="AC13" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AD13" t="s" s="2">
         <v>81</v>
@@ -4365,7 +4371,7 @@
         <v>139</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>79</v>
@@ -4397,10 +4403,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -4426,13 +4432,13 @@
         <v>104</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -4440,7 +4446,7 @@
       </c>
       <c r="Q14" s="2"/>
       <c r="R14" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="S14" t="s" s="2">
         <v>81</v>
@@ -4482,7 +4488,7 @@
         <v>81</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>90</v>
@@ -4514,17 +4520,17 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
         <v>81</v>
       </c>
       <c r="E15" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F15" t="s" s="2">
         <v>79</v>
@@ -4542,13 +4548,13 @@
         <v>81</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -4575,13 +4581,13 @@
         <v>81</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>81</v>
@@ -4599,7 +4605,7 @@
         <v>81</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>79</v>
@@ -4631,10 +4637,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -4657,13 +4663,13 @@
         <v>81</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -4714,7 +4720,7 @@
         <v>81</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>79</v>
@@ -4735,7 +4741,7 @@
         <v>81</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AN16" t="s" s="2">
         <v>81</v>
@@ -4746,14 +4752,14 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -4775,13 +4781,13 @@
         <v>135</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -4822,7 +4828,7 @@
         <v>138</v>
       </c>
       <c r="AC17" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AD17" t="s" s="2">
         <v>81</v>
@@ -4831,7 +4837,7 @@
         <v>139</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>79</v>
@@ -4852,7 +4858,7 @@
         <v>81</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>81</v>
@@ -4863,10 +4869,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4889,19 +4895,19 @@
         <v>91</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O18" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>81</v>
@@ -4950,7 +4956,7 @@
         <v>81</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>79</v>
@@ -4971,21 +4977,21 @@
         <v>81</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -5008,19 +5014,19 @@
         <v>91</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>81</v>
@@ -5069,7 +5075,7 @@
         <v>81</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>79</v>
@@ -5090,25 +5096,25 @@
         <v>81</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -5130,16 +5136,16 @@
         <v>135</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>81</v>
@@ -5188,7 +5194,7 @@
         <v>81</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>79</v>
@@ -5220,10 +5226,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -5246,16 +5252,16 @@
         <v>81</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -5305,7 +5311,7 @@
         <v>81</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>79</v>
@@ -5320,27 +5326,27 @@
         <v>102</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -5366,13 +5372,13 @@
         <v>110</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -5398,13 +5404,13 @@
         <v>81</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>81</v>
@@ -5422,7 +5428,7 @@
         <v>81</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>90</v>
@@ -5437,16 +5443,16 @@
         <v>102</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>81</v>
@@ -5454,10 +5460,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -5480,16 +5486,16 @@
         <v>81</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -5515,13 +5521,13 @@
         <v>81</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>81</v>
@@ -5539,7 +5545,7 @@
         <v>81</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>79</v>
@@ -5554,13 +5560,13 @@
         <v>102</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>81</v>
@@ -5571,10 +5577,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5600,13 +5606,13 @@
         <v>110</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -5632,13 +5638,13 @@
         <v>81</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>81</v>
@@ -5656,7 +5662,7 @@
         <v>81</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>90</v>
@@ -5671,16 +5677,16 @@
         <v>102</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>81</v>
@@ -5688,10 +5694,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5714,16 +5720,16 @@
         <v>81</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -5749,13 +5755,13 @@
         <v>81</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>81</v>
@@ -5773,7 +5779,7 @@
         <v>81</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>79</v>
@@ -5791,13 +5797,13 @@
         <v>81</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>81</v>
@@ -5805,10 +5811,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5834,10 +5840,10 @@
         <v>110</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -5864,13 +5870,13 @@
         <v>81</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>81</v>
@@ -5888,7 +5894,7 @@
         <v>81</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
@@ -5903,16 +5909,16 @@
         <v>102</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>81</v>
@@ -5920,10 +5926,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5946,16 +5952,16 @@
         <v>91</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -6005,7 +6011,7 @@
         <v>81</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>
@@ -6026,7 +6032,7 @@
         <v>81</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>81</v>
@@ -6037,10 +6043,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -6063,13 +6069,13 @@
         <v>91</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -6120,7 +6126,7 @@
         <v>81</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
@@ -6141,7 +6147,7 @@
         <v>81</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>81</v>
@@ -6152,10 +6158,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -6178,16 +6184,16 @@
         <v>91</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -6213,29 +6219,29 @@
         <v>81</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AC29" s="2"/>
       <c r="AD29" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>90</v>
@@ -6250,30 +6256,30 @@
         <v>102</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C30" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D30" t="s" s="2">
         <v>81</v>
@@ -6295,16 +6301,16 @@
         <v>91</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -6354,7 +6360,7 @@
         <v>81</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>90</v>
@@ -6369,30 +6375,30 @@
         <v>102</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C31" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D31" t="s" s="2">
         <v>81</v>
@@ -6414,16 +6420,16 @@
         <v>91</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -6449,11 +6455,11 @@
         <v>81</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Y31" s="2"/>
       <c r="Z31" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>81</v>
@@ -6471,7 +6477,7 @@
         <v>81</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>90</v>
@@ -6486,27 +6492,27 @@
         <v>102</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6529,16 +6535,16 @@
         <v>91</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -6588,7 +6594,7 @@
         <v>81</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>90</v>
@@ -6603,27 +6609,27 @@
         <v>102</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6646,16 +6652,16 @@
         <v>81</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -6705,7 +6711,7 @@
         <v>81</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
@@ -6720,27 +6726,27 @@
         <v>102</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6763,13 +6769,13 @@
         <v>81</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -6820,7 +6826,7 @@
         <v>81</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
@@ -6835,16 +6841,16 @@
         <v>102</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>81</v>
@@ -6852,10 +6858,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6878,13 +6884,13 @@
         <v>91</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -6935,7 +6941,7 @@
         <v>81</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
@@ -6950,27 +6956,27 @@
         <v>102</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6993,13 +6999,13 @@
         <v>91</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -7050,7 +7056,7 @@
         <v>81</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
@@ -7065,16 +7071,16 @@
         <v>102</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>81</v>
@@ -7082,10 +7088,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -7108,13 +7114,13 @@
         <v>81</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -7165,7 +7171,7 @@
         <v>81</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -7180,16 +7186,16 @@
         <v>102</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>81</v>
@@ -7197,10 +7203,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -7223,16 +7229,16 @@
         <v>91</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -7258,13 +7264,13 @@
         <v>81</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>81</v>
@@ -7282,7 +7288,7 @@
         <v>81</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
@@ -7297,13 +7303,13 @@
         <v>102</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>81</v>
@@ -7314,10 +7320,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7340,13 +7346,13 @@
         <v>81</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -7397,7 +7403,7 @@
         <v>81</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
@@ -7418,10 +7424,10 @@
         <v>81</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>81</v>
@@ -7429,10 +7435,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7455,16 +7461,16 @@
         <v>81</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -7490,13 +7496,13 @@
         <v>81</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>81</v>
@@ -7514,7 +7520,7 @@
         <v>81</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
@@ -7529,27 +7535,27 @@
         <v>102</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7572,16 +7578,16 @@
         <v>81</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -7631,7 +7637,7 @@
         <v>81</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
@@ -7646,16 +7652,16 @@
         <v>102</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>81</v>
@@ -7663,10 +7669,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7689,13 +7695,13 @@
         <v>91</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -7746,7 +7752,7 @@
         <v>81</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
@@ -7761,13 +7767,13 @@
         <v>102</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>81</v>
@@ -7778,10 +7784,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7807,10 +7813,10 @@
         <v>104</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -7861,7 +7867,7 @@
         <v>81</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
@@ -7882,7 +7888,7 @@
         <v>81</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>81</v>
@@ -7893,10 +7899,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7919,13 +7925,13 @@
         <v>91</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7976,7 +7982,7 @@
         <v>81</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
@@ -7991,13 +7997,13 @@
         <v>102</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>81</v>
@@ -8008,10 +8014,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -8034,17 +8040,17 @@
         <v>91</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>81</v>
@@ -8093,7 +8099,7 @@
         <v>81</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
@@ -8108,13 +8114,13 @@
         <v>102</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>81</v>
@@ -8125,10 +8131,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8151,16 +8157,16 @@
         <v>81</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -8186,13 +8192,13 @@
         <v>81</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>81</v>
@@ -8210,7 +8216,7 @@
         <v>81</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -8231,7 +8237,7 @@
         <v>81</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>81</v>
@@ -8242,10 +8248,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8268,13 +8274,13 @@
         <v>81</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -8325,7 +8331,7 @@
         <v>81</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
@@ -8340,13 +8346,13 @@
         <v>102</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>81</v>
@@ -8357,10 +8363,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8383,13 +8389,13 @@
         <v>81</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -8440,7 +8446,7 @@
         <v>81</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
@@ -8455,13 +8461,13 @@
         <v>102</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>81</v>
@@ -8472,10 +8478,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8498,16 +8504,16 @@
         <v>81</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -8557,7 +8563,7 @@
         <v>81</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>79</v>
@@ -8572,13 +8578,13 @@
         <v>102</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>81</v>
@@ -8589,10 +8595,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8615,13 +8621,13 @@
         <v>81</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -8672,7 +8678,7 @@
         <v>81</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
@@ -8693,7 +8699,7 @@
         <v>81</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>81</v>
@@ -8704,14 +8710,14 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -8733,13 +8739,13 @@
         <v>135</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8780,7 +8786,7 @@
         <v>138</v>
       </c>
       <c r="AC51" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AD51" t="s" s="2">
         <v>81</v>
@@ -8789,7 +8795,7 @@
         <v>139</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
@@ -8810,7 +8816,7 @@
         <v>81</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>81</v>
@@ -8821,14 +8827,14 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -8850,16 +8856,16 @@
         <v>135</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>81</v>
@@ -8908,7 +8914,7 @@
         <v>81</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
@@ -8940,10 +8946,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8966,17 +8972,17 @@
         <v>91</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>81</v>
@@ -9025,7 +9031,7 @@
         <v>81</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
@@ -9046,21 +9052,21 @@
         <v>81</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9083,17 +9089,17 @@
         <v>91</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>81</v>
@@ -9142,7 +9148,7 @@
         <v>81</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -9163,21 +9169,21 @@
         <v>81</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9200,19 +9206,19 @@
         <v>91</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>81</v>
@@ -9237,13 +9243,13 @@
         <v>81</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>81</v>
@@ -9261,7 +9267,7 @@
         <v>81</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -9282,21 +9288,21 @@
         <v>81</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9319,13 +9325,13 @@
         <v>91</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -9376,7 +9382,7 @@
         <v>81</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
@@ -9397,21 +9403,21 @@
         <v>81</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9434,19 +9440,19 @@
         <v>91</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>81</v>
@@ -9495,7 +9501,7 @@
         <v>81</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
@@ -9516,7 +9522,7 @@
         <v>81</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>81</v>
@@ -9527,10 +9533,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9553,13 +9559,13 @@
         <v>81</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -9610,7 +9616,7 @@
         <v>81</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
@@ -9631,7 +9637,7 @@
         <v>81</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>81</v>
@@ -9642,14 +9648,14 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -9671,13 +9677,13 @@
         <v>135</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -9718,7 +9724,7 @@
         <v>138</v>
       </c>
       <c r="AC59" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AD59" t="s" s="2">
         <v>81</v>
@@ -9727,7 +9733,7 @@
         <v>139</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
@@ -9748,7 +9754,7 @@
         <v>81</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>81</v>
@@ -9759,14 +9765,14 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -9788,16 +9794,16 @@
         <v>135</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>81</v>
@@ -9846,7 +9852,7 @@
         <v>81</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
@@ -9878,10 +9884,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9904,17 +9910,17 @@
         <v>91</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>81</v>
@@ -9963,7 +9969,7 @@
         <v>81</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
@@ -9984,7 +9990,7 @@
         <v>81</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>81</v>
@@ -9995,10 +10001,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10021,17 +10027,17 @@
         <v>91</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>81</v>
@@ -10080,7 +10086,7 @@
         <v>81</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
@@ -10092,7 +10098,7 @@
         <v>81</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>81</v>
@@ -10101,7 +10107,7 @@
         <v>81</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>81</v>
@@ -10112,10 +10118,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10138,13 +10144,13 @@
         <v>81</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -10195,7 +10201,7 @@
         <v>81</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>79</v>
@@ -10216,7 +10222,7 @@
         <v>81</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>81</v>
@@ -10227,14 +10233,14 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
@@ -10256,13 +10262,13 @@
         <v>135</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -10303,7 +10309,7 @@
         <v>138</v>
       </c>
       <c r="AC64" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AD64" t="s" s="2">
         <v>81</v>
@@ -10312,7 +10318,7 @@
         <v>139</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
@@ -10333,7 +10339,7 @@
         <v>81</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>81</v>
@@ -10344,13 +10350,13 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="B65" t="s" s="2">
         <v>487</v>
       </c>
-      <c r="B65" t="s" s="2">
-        <v>486</v>
-      </c>
       <c r="C65" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="D65" t="s" s="2">
         <v>81</v>
@@ -10372,13 +10378,13 @@
         <v>81</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -10429,7 +10435,7 @@
         <v>81</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
@@ -10461,10 +10467,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10487,13 +10493,13 @@
         <v>91</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -10544,7 +10550,7 @@
         <v>81</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
@@ -10565,7 +10571,7 @@
         <v>81</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>81</v>
@@ -10576,10 +10582,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10602,19 +10608,19 @@
         <v>91</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>81</v>
@@ -10663,7 +10669,7 @@
         <v>81</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
@@ -10684,7 +10690,7 @@
         <v>81</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>81</v>
@@ -10695,10 +10701,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10721,13 +10727,13 @@
         <v>91</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -10778,7 +10784,7 @@
         <v>81</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>79</v>
@@ -10799,7 +10805,7 @@
         <v>81</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>81</v>
@@ -10810,10 +10816,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10836,19 +10842,19 @@
         <v>91</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>81</v>
@@ -10897,7 +10903,7 @@
         <v>81</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
@@ -10918,7 +10924,7 @@
         <v>81</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>81</v>
@@ -10929,10 +10935,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10955,19 +10961,19 @@
         <v>91</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>81</v>
@@ -11016,7 +11022,7 @@
         <v>81</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>79</v>
@@ -11037,7 +11043,7 @@
         <v>81</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>81</v>
@@ -11048,10 +11054,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11077,10 +11083,10 @@
         <v>110</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -11107,13 +11113,13 @@
         <v>81</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>81</v>
@@ -11131,7 +11137,7 @@
         <v>81</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
@@ -11152,7 +11158,7 @@
         <v>81</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>81</v>
@@ -11163,10 +11169,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11189,13 +11195,13 @@
         <v>91</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -11203,7 +11209,7 @@
         <v>81</v>
       </c>
       <c r="Q72" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="R72" t="s" s="2">
         <v>81</v>
@@ -11248,7 +11254,7 @@
         <v>81</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
@@ -11269,7 +11275,7 @@
         <v>81</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>81</v>
@@ -11280,10 +11286,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11306,13 +11312,13 @@
         <v>91</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -11363,7 +11369,7 @@
         <v>81</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>79</v>
@@ -11384,7 +11390,7 @@
         <v>81</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>81</v>
@@ -11395,10 +11401,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11421,13 +11427,13 @@
         <v>91</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -11478,7 +11484,7 @@
         <v>81</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>79</v>
@@ -11499,7 +11505,7 @@
         <v>81</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>81</v>
@@ -11510,10 +11516,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11536,13 +11542,13 @@
         <v>91</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -11593,7 +11599,7 @@
         <v>81</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>79</v>
@@ -11614,7 +11620,7 @@
         <v>81</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>81</v>
@@ -11625,10 +11631,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11654,10 +11660,10 @@
         <v>110</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -11684,13 +11690,13 @@
         <v>81</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>81</v>
@@ -11708,7 +11714,7 @@
         <v>81</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>79</v>
@@ -11729,7 +11735,7 @@
         <v>81</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="AN76" t="s" s="2">
         <v>81</v>
@@ -11740,10 +11746,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11769,13 +11775,13 @@
         <v>110</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -11801,11 +11807,11 @@
         <v>81</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Y77" s="2"/>
       <c r="Z77" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>81</v>
@@ -11823,7 +11829,7 @@
         <v>81</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>79</v>
@@ -11844,7 +11850,7 @@
         <v>81</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AN77" t="s" s="2">
         <v>81</v>
@@ -11855,10 +11861,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11881,16 +11887,16 @@
         <v>91</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -11940,7 +11946,7 @@
         <v>81</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>79</v>
@@ -11961,7 +11967,7 @@
         <v>81</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>81</v>
@@ -11972,10 +11978,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -12001,16 +12007,16 @@
         <v>110</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="O79" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>81</v>
@@ -12035,13 +12041,13 @@
         <v>81</v>
       </c>
       <c r="X79" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Y79" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="Z79" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>81</v>
@@ -12059,7 +12065,7 @@
         <v>81</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>79</v>
@@ -12080,7 +12086,7 @@
         <v>81</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="AN79" t="s" s="2">
         <v>81</v>
@@ -12091,10 +12097,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12117,13 +12123,13 @@
         <v>91</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -12174,7 +12180,7 @@
         <v>81</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>79</v>
@@ -12195,7 +12201,7 @@
         <v>81</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="AN80" t="s" s="2">
         <v>81</v>
@@ -12206,10 +12212,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12232,16 +12238,16 @@
         <v>91</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -12270,10 +12276,10 @@
         <v>114</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="Z81" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>81</v>
@@ -12291,7 +12297,7 @@
         <v>81</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>79</v>
@@ -12312,7 +12318,7 @@
         <v>81</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="AN81" t="s" s="2">
         <v>81</v>
@@ -12323,10 +12329,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12349,16 +12355,16 @@
         <v>91</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -12384,13 +12390,13 @@
         <v>81</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>81</v>
@@ -12408,7 +12414,7 @@
         <v>81</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>79</v>
@@ -12429,21 +12435,21 @@
         <v>81</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="AN82" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO82" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12466,19 +12472,19 @@
         <v>91</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>81</v>
@@ -12503,13 +12509,13 @@
         <v>81</v>
       </c>
       <c r="X83" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Y83" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="Z83" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>81</v>
@@ -12527,7 +12533,7 @@
         <v>81</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>79</v>
@@ -12548,21 +12554,21 @@
         <v>81</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="AN83" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO83" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12585,17 +12591,17 @@
         <v>91</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>81</v>
@@ -12620,11 +12626,11 @@
         <v>81</v>
       </c>
       <c r="X84" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Y84" s="2"/>
       <c r="Z84" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>81</v>
@@ -12642,7 +12648,7 @@
         <v>81</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>79</v>
@@ -12663,21 +12669,21 @@
         <v>81</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="AN84" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO84" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12700,19 +12706,19 @@
         <v>91</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="O85" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>81</v>
@@ -12737,11 +12743,11 @@
         <v>81</v>
       </c>
       <c r="X85" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Y85" s="2"/>
       <c r="Z85" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="AA85" t="s" s="2">
         <v>81</v>
@@ -12759,7 +12765,7 @@
         <v>81</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>79</v>
@@ -12780,21 +12786,21 @@
         <v>81</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="AN85" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO85" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12817,13 +12823,13 @@
         <v>91</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -12874,7 +12880,7 @@
         <v>81</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>79</v>
@@ -12901,15 +12907,15 @@
         <v>81</v>
       </c>
       <c r="AO86" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12932,13 +12938,13 @@
         <v>81</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -12989,7 +12995,7 @@
         <v>81</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>79</v>
@@ -13010,7 +13016,7 @@
         <v>81</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AN87" t="s" s="2">
         <v>81</v>
@@ -13021,14 +13027,14 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
@@ -13050,13 +13056,13 @@
         <v>135</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
@@ -13097,7 +13103,7 @@
         <v>138</v>
       </c>
       <c r="AC88" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AD88" t="s" s="2">
         <v>81</v>
@@ -13106,7 +13112,7 @@
         <v>139</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>79</v>
@@ -13127,7 +13133,7 @@
         <v>81</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AN88" t="s" s="2">
         <v>81</v>
@@ -13138,13 +13144,13 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
+        <v>628</v>
+      </c>
+      <c r="B89" t="s" s="2">
         <v>627</v>
       </c>
-      <c r="B89" t="s" s="2">
-        <v>626</v>
-      </c>
       <c r="C89" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="D89" t="s" s="2">
         <v>81</v>
@@ -13166,13 +13172,13 @@
         <v>81</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -13223,7 +13229,7 @@
         <v>81</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>79</v>
@@ -13255,10 +13261,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13281,17 +13287,17 @@
         <v>91</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>81</v>
@@ -13316,13 +13322,13 @@
         <v>81</v>
       </c>
       <c r="X90" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Y90" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="Z90" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>81</v>
@@ -13340,7 +13346,7 @@
         <v>81</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>79</v>
@@ -13367,15 +13373,15 @@
         <v>81</v>
       </c>
       <c r="AO90" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13398,19 +13404,19 @@
         <v>91</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>81</v>
@@ -13447,17 +13453,17 @@
         <v>81</v>
       </c>
       <c r="AB91" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AC91" s="2"/>
       <c r="AD91" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE91" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>79</v>
@@ -13478,24 +13484,24 @@
         <v>81</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="AN91" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO91" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="C92" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="D92" t="s" s="2">
         <v>81</v>
@@ -13517,19 +13523,19 @@
         <v>91</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>81</v>
@@ -13578,7 +13584,7 @@
         <v>81</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>79</v>
@@ -13599,24 +13605,24 @@
         <v>81</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="AN92" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO92" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="C93" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="D93" t="s" s="2">
         <v>81</v>
@@ -13638,19 +13644,19 @@
         <v>91</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>81</v>
@@ -13699,7 +13705,7 @@
         <v>81</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>79</v>
@@ -13720,21 +13726,21 @@
         <v>81</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="AN93" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO93" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13757,19 +13763,19 @@
         <v>91</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>81</v>
@@ -13806,17 +13812,17 @@
         <v>81</v>
       </c>
       <c r="AB94" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AC94" s="2"/>
       <c r="AD94" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE94" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>79</v>
@@ -13837,24 +13843,24 @@
         <v>81</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="AN94" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO94" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="C95" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="D95" t="s" s="2">
         <v>81</v>
@@ -13876,19 +13882,19 @@
         <v>91</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="O95" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>81</v>
@@ -13937,7 +13943,7 @@
         <v>81</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>79</v>
@@ -13958,24 +13964,24 @@
         <v>81</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="AN95" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO95" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="C96" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="D96" t="s" s="2">
         <v>81</v>
@@ -13997,19 +14003,19 @@
         <v>91</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="O96" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>81</v>
@@ -14058,7 +14064,7 @@
         <v>81</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>79</v>
@@ -14079,24 +14085,24 @@
         <v>81</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="AN96" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO96" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="C97" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="D97" t="s" s="2">
         <v>81</v>
@@ -14118,19 +14124,19 @@
         <v>91</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="O97" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>81</v>
@@ -14179,7 +14185,7 @@
         <v>81</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>79</v>
@@ -14200,21 +14206,21 @@
         <v>81</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="AN97" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO97" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14237,19 +14243,19 @@
         <v>91</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="O98" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>81</v>
@@ -14298,7 +14304,7 @@
         <v>81</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>79</v>
@@ -14319,21 +14325,21 @@
         <v>81</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="AN98" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO98" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14356,13 +14362,13 @@
         <v>81</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" s="2"/>
@@ -14413,7 +14419,7 @@
         <v>81</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>79</v>
@@ -14434,7 +14440,7 @@
         <v>81</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AN99" t="s" s="2">
         <v>81</v>
@@ -14445,14 +14451,14 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E100" s="2"/>
       <c r="F100" t="s" s="2">
@@ -14474,13 +14480,13 @@
         <v>135</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
@@ -14521,7 +14527,7 @@
         <v>138</v>
       </c>
       <c r="AC100" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AD100" t="s" s="2">
         <v>81</v>
@@ -14530,7 +14536,7 @@
         <v>139</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>79</v>
@@ -14551,7 +14557,7 @@
         <v>81</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AN100" t="s" s="2">
         <v>81</v>
@@ -14562,10 +14568,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14588,13 +14594,13 @@
         <v>91</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="N101" s="2"/>
       <c r="O101" s="2"/>
@@ -14645,7 +14651,7 @@
         <v>81</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>79</v>
@@ -14666,7 +14672,7 @@
         <v>81</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="AN101" t="s" s="2">
         <v>81</v>
@@ -14677,10 +14683,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14703,13 +14709,13 @@
         <v>91</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
@@ -14760,7 +14766,7 @@
         <v>81</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>79</v>
@@ -14781,7 +14787,7 @@
         <v>81</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="AN102" t="s" s="2">
         <v>81</v>
@@ -14792,10 +14798,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14818,19 +14824,19 @@
         <v>91</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="O103" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>81</v>
@@ -14879,7 +14885,7 @@
         <v>81</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>79</v>
@@ -14900,7 +14906,7 @@
         <v>81</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="AN103" t="s" s="2">
         <v>81</v>
@@ -14911,10 +14917,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14937,17 +14943,17 @@
         <v>91</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>81</v>
@@ -14996,7 +15002,7 @@
         <v>81</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>79</v>
@@ -15017,7 +15023,7 @@
         <v>81</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="AN104" t="s" s="2">
         <v>81</v>
@@ -15028,10 +15034,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15054,13 +15060,13 @@
         <v>81</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" s="2"/>
@@ -15111,7 +15117,7 @@
         <v>81</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>79</v>
@@ -15129,10 +15135,10 @@
         <v>81</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="AM105" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="AN105" t="s" s="2">
         <v>81</v>
@@ -15143,10 +15149,10 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -15169,13 +15175,13 @@
         <v>81</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" s="2"/>
@@ -15226,7 +15232,7 @@
         <v>81</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>79</v>
@@ -15247,7 +15253,7 @@
         <v>81</v>
       </c>
       <c r="AM106" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AN106" t="s" s="2">
         <v>81</v>
@@ -15258,14 +15264,14 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E107" s="2"/>
       <c r="F107" t="s" s="2">
@@ -15287,13 +15293,13 @@
         <v>135</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
@@ -15343,7 +15349,7 @@
         <v>81</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>79</v>
@@ -15364,7 +15370,7 @@
         <v>81</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AN107" t="s" s="2">
         <v>81</v>
@@ -15375,14 +15381,14 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E108" s="2"/>
       <c r="F108" t="s" s="2">
@@ -15404,16 +15410,16 @@
         <v>135</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="O108" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>81</v>
@@ -15462,7 +15468,7 @@
         <v>81</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>79</v>
@@ -15494,10 +15500,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15520,16 +15526,16 @@
         <v>81</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
@@ -15579,7 +15585,7 @@
         <v>81</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>79</v>
@@ -15600,7 +15606,7 @@
         <v>81</v>
       </c>
       <c r="AM109" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="AN109" t="s" s="2">
         <v>81</v>
@@ -15611,10 +15617,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15637,13 +15643,13 @@
         <v>81</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="N110" s="2"/>
       <c r="O110" s="2"/>
@@ -15694,7 +15700,7 @@
         <v>81</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>79</v>
@@ -15715,7 +15721,7 @@
         <v>81</v>
       </c>
       <c r="AM110" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AN110" t="s" s="2">
         <v>81</v>
@@ -15726,14 +15732,14 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E111" s="2"/>
       <c r="F111" t="s" s="2">
@@ -15755,13 +15761,13 @@
         <v>135</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
@@ -15811,7 +15817,7 @@
         <v>81</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>79</v>
@@ -15832,7 +15838,7 @@
         <v>81</v>
       </c>
       <c r="AM111" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AN111" t="s" s="2">
         <v>81</v>
@@ -15843,14 +15849,14 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E112" s="2"/>
       <c r="F112" t="s" s="2">
@@ -15872,16 +15878,16 @@
         <v>135</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="O112" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P112" t="s" s="2">
         <v>81</v>
@@ -15930,7 +15936,7 @@
         <v>81</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>79</v>
@@ -15962,10 +15968,10 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15988,13 +15994,13 @@
         <v>81</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="N113" s="2"/>
       <c r="O113" s="2"/>
@@ -16045,7 +16051,7 @@
         <v>81</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>79</v>
@@ -16066,7 +16072,7 @@
         <v>81</v>
       </c>
       <c r="AM113" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="AN113" t="s" s="2">
         <v>81</v>
@@ -16077,10 +16083,10 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -16103,13 +16109,13 @@
         <v>81</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="N114" s="2"/>
       <c r="O114" s="2"/>
@@ -16160,7 +16166,7 @@
         <v>81</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>79</v>
@@ -16181,7 +16187,7 @@
         <v>81</v>
       </c>
       <c r="AM114" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="AN114" t="s" s="2">
         <v>81</v>
@@ -16192,10 +16198,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16218,13 +16224,13 @@
         <v>81</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="N115" s="2"/>
       <c r="O115" s="2"/>
@@ -16275,7 +16281,7 @@
         <v>81</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>79</v>
@@ -16296,7 +16302,7 @@
         <v>81</v>
       </c>
       <c r="AM115" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="AN115" t="s" s="2">
         <v>81</v>
@@ -16307,10 +16313,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16333,19 +16339,19 @@
         <v>81</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="N116" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="O116" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="P116" t="s" s="2">
         <v>81</v>
@@ -16394,7 +16400,7 @@
         <v>81</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>79</v>
@@ -16412,10 +16418,10 @@
         <v>81</v>
       </c>
       <c r="AL116" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="AM116" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="AN116" t="s" s="2">
         <v>81</v>
@@ -16426,10 +16432,10 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16452,16 +16458,16 @@
         <v>81</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="N117" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="O117" s="2"/>
       <c r="P117" t="s" s="2">
@@ -16511,7 +16517,7 @@
         <v>81</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>79</v>
@@ -16529,24 +16535,24 @@
         <v>81</v>
       </c>
       <c r="AL117" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="AM117" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="AN117" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO117" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16569,13 +16575,13 @@
         <v>81</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="N118" s="2"/>
       <c r="O118" s="2"/>
@@ -16626,7 +16632,7 @@
         <v>81</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>79</v>
@@ -16644,24 +16650,24 @@
         <v>81</v>
       </c>
       <c r="AL118" t="s" s="2">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="AM118" t="s" s="2">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="AN118" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO118" t="s" s="2">
-        <v>754</v>
+        <v>755</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16684,16 +16690,16 @@
         <v>81</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="N119" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="O119" s="2"/>
       <c r="P119" t="s" s="2">
@@ -16743,7 +16749,7 @@
         <v>81</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>79</v>
@@ -16761,10 +16767,10 @@
         <v>81</v>
       </c>
       <c r="AL119" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="AM119" t="s" s="2">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="AN119" t="s" s="2">
         <v>81</v>
@@ -16775,10 +16781,10 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16801,13 +16807,13 @@
         <v>81</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="N120" s="2"/>
       <c r="O120" s="2"/>
@@ -16858,7 +16864,7 @@
         <v>81</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>79</v>
@@ -16879,10 +16885,10 @@
         <v>81</v>
       </c>
       <c r="AM120" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="AN120" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AO120" t="s" s="2">
         <v>81</v>
@@ -16890,10 +16896,10 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -16916,13 +16922,13 @@
         <v>81</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="N121" s="2"/>
       <c r="O121" s="2"/>
@@ -16973,7 +16979,7 @@
         <v>81</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>79</v>
@@ -16991,10 +16997,10 @@
         <v>81</v>
       </c>
       <c r="AL121" t="s" s="2">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="AM121" t="s" s="2">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="AN121" t="s" s="2">
         <v>81</v>
@@ -17005,10 +17011,10 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -17031,13 +17037,13 @@
         <v>81</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="N122" s="2"/>
       <c r="O122" s="2"/>
@@ -17088,7 +17094,7 @@
         <v>81</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>79</v>
@@ -17109,7 +17115,7 @@
         <v>81</v>
       </c>
       <c r="AM122" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AN122" t="s" s="2">
         <v>81</v>
@@ -17120,14 +17126,14 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E123" s="2"/>
       <c r="F123" t="s" s="2">
@@ -17149,13 +17155,13 @@
         <v>135</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="N123" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="O123" s="2"/>
       <c r="P123" t="s" s="2">
@@ -17205,7 +17211,7 @@
         <v>81</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>79</v>
@@ -17226,7 +17232,7 @@
         <v>81</v>
       </c>
       <c r="AM123" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AN123" t="s" s="2">
         <v>81</v>
@@ -17237,14 +17243,14 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E124" s="2"/>
       <c r="F124" t="s" s="2">
@@ -17266,16 +17272,16 @@
         <v>135</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="N124" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="O124" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P124" t="s" s="2">
         <v>81</v>
@@ -17324,7 +17330,7 @@
         <v>81</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>79</v>
@@ -17356,10 +17362,10 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -17382,16 +17388,16 @@
         <v>81</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="O125" s="2"/>
       <c r="P125" t="s" s="2">
@@ -17417,13 +17423,13 @@
         <v>81</v>
       </c>
       <c r="X125" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Y125" t="s" s="2">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="Z125" t="s" s="2">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="AA125" t="s" s="2">
         <v>81</v>
@@ -17441,7 +17447,7 @@
         <v>81</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>90</v>
@@ -17459,24 +17465,24 @@
         <v>81</v>
       </c>
       <c r="AL125" t="s" s="2">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="AM125" t="s" s="2">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="AN125" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO125" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -17499,13 +17505,13 @@
         <v>81</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="N126" s="2"/>
       <c r="O126" s="2"/>
@@ -17532,13 +17538,13 @@
         <v>81</v>
       </c>
       <c r="X126" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Y126" t="s" s="2">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="Z126" t="s" s="2">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="AA126" t="s" s="2">
         <v>81</v>
@@ -17556,7 +17562,7 @@
         <v>81</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>79</v>
@@ -17574,24 +17580,24 @@
         <v>81</v>
       </c>
       <c r="AL126" t="s" s="2">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="AM126" t="s" s="2">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="AN126" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO126" t="s" s="2">
-        <v>789</v>
+        <v>790</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17614,13 +17620,13 @@
         <v>81</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="N127" s="2"/>
       <c r="O127" s="2"/>
@@ -17671,7 +17677,7 @@
         <v>81</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>79</v>
@@ -17686,13 +17692,13 @@
         <v>102</v>
       </c>
       <c r="AK127" t="s" s="2">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="AL127" t="s" s="2">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="AM127" t="s" s="2">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="AN127" t="s" s="2">
         <v>81</v>
@@ -17703,14 +17709,14 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="E128" s="2"/>
       <c r="F128" t="s" s="2">
@@ -17729,16 +17735,16 @@
         <v>81</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="N128" t="s" s="2">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="O128" s="2"/>
       <c r="P128" t="s" s="2">
@@ -17788,7 +17794,7 @@
         <v>81</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>79</v>
@@ -17809,7 +17815,7 @@
         <v>81</v>
       </c>
       <c r="AM128" t="s" s="2">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="AN128" t="s" s="2">
         <v>81</v>
@@ -17820,10 +17826,10 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -17846,16 +17852,16 @@
         <v>81</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="N129" t="s" s="2">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="O129" s="2"/>
       <c r="P129" t="s" s="2">
@@ -17905,7 +17911,7 @@
         <v>81</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>79</v>
@@ -17920,13 +17926,13 @@
         <v>102</v>
       </c>
       <c r="AK129" t="s" s="2">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="AL129" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM129" t="s" s="2">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="AN129" t="s" s="2">
         <v>81</v>

--- a/AnalysePharma/ig/StructureDefinition-fr-medicationrequest.xlsx
+++ b/AnalysePharma/ig/StructureDefinition-fr-medicationrequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-30T09:49:26+00:00</t>
+    <t>2026-05-12T12:57:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/AnalysePharma/ig/StructureDefinition-fr-medicationrequest.xlsx
+++ b/AnalysePharma/ig/StructureDefinition-fr-medicationrequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-12T12:57:02+00:00</t>
+    <t>2026-05-12T16:45:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/AnalysePharma/ig/StructureDefinition-fr-medicationrequest.xlsx
+++ b/AnalysePharma/ig/StructureDefinition-fr-medicationrequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-12T16:45:43+00:00</t>
+    <t>2026-05-18T17:19:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
